--- a/excel/Diet.xlsx
+++ b/excel/Diet.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\boyko\stats\opt2025\excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Boyko Amarov\stats\opt2026\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00DF482C-BB7A-47C8-A81B-24A02118CFE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25B0FCDE-DF6E-4BF2-902E-268C4EFA312B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1536" yWindow="1536" windowWidth="17280" windowHeight="9960" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="27000" yWindow="4695" windowWidth="22725" windowHeight="11760" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Answer Report 1" sheetId="2" r:id="rId1"/>
@@ -481,7 +481,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -504,10 +504,9 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -811,82 +810,81 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{090165B0-D215-4524-B96D-F9D129D81244}">
   <dimension ref="A1:G37"/>
-  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="2.33203125" customWidth="1"/>
-    <col min="2" max="2" width="6.21875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.44140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.6640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.77734375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.28515625" customWidth="1"/>
+    <col min="2" max="2" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.42578125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2"/>
       <c r="B6" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="7" spans="1:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2"/>
       <c r="B7" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="8" spans="1:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2"/>
       <c r="B8" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="9" spans="1:5" collapsed="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" collapsed="1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="10" spans="1:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="11" spans="1:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="1:5" collapsed="1" x14ac:dyDescent="0.3"/>
-    <row r="14" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:5" collapsed="1" x14ac:dyDescent="0.25"/>
+    <row r="14" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B15" s="4" t="s">
         <v>27</v>
       </c>
@@ -900,7 +898,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="16" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B16" s="3" t="s">
         <v>38</v>
       </c>
@@ -914,12 +912,12 @@
         <v>68.181818181818187</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B20" s="4" t="s">
         <v>27</v>
       </c>
@@ -936,7 +934,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B21" s="7" t="s">
         <v>64</v>
       </c>
@@ -945,7 +943,7 @@
       <c r="E21" s="6"/>
       <c r="F21" s="6"/>
     </row>
-    <row r="22" spans="1:7" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B22" s="5" t="s">
         <v>40</v>
       </c>
@@ -962,7 +960,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="23" spans="1:7" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B23" s="5" t="s">
         <v>43</v>
       </c>
@@ -979,7 +977,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="24" spans="1:7" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B24" s="5" t="s">
         <v>45</v>
       </c>
@@ -996,7 +994,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="25" spans="1:7" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B25" s="5" t="s">
         <v>47</v>
       </c>
@@ -1013,7 +1011,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="26" spans="1:7" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B26" s="5" t="s">
         <v>49</v>
       </c>
@@ -1030,7 +1028,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="15" hidden="1" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:7" ht="15.75" hidden="1" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B27" s="3" t="s">
         <v>51</v>
       </c>
@@ -1047,13 +1045,13 @@
         <v>42</v>
       </c>
     </row>
-    <row r="28" spans="1:7" collapsed="1" x14ac:dyDescent="0.3"/>
-    <row r="31" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:7" collapsed="1" x14ac:dyDescent="0.25"/>
+    <row r="31" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="32" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B32" s="4" t="s">
         <v>27</v>
       </c>
@@ -1073,7 +1071,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="33" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B33" s="7" t="s">
         <v>65</v>
       </c>
@@ -1083,7 +1081,7 @@
       <c r="F33" s="6"/>
       <c r="G33" s="6"/>
     </row>
-    <row r="34" spans="2:7" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="2:7" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B34" s="5" t="s">
         <v>53</v>
       </c>
@@ -1103,7 +1101,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="2:7" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:7" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B35" s="5" t="s">
         <v>57</v>
       </c>
@@ -1123,7 +1121,7 @@
         <v>10.909090909090921</v>
       </c>
     </row>
-    <row r="36" spans="2:7" ht="15" hidden="1" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="2:7" ht="15.75" hidden="1" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B36" s="3" t="s">
         <v>61</v>
       </c>
@@ -1143,7 +1141,7 @@
         <v>37.45454545454546</v>
       </c>
     </row>
-    <row r="37" spans="2:7" collapsed="1" x14ac:dyDescent="0.3"/>
+    <row r="37" spans="2:7" collapsed="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1152,37 +1150,37 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BBE2A7D5-5C0D-4672-BAC3-F2FBA686E6CD}">
   <dimension ref="A1:H25"/>
-  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="2.33203125" customWidth="1"/>
-    <col min="2" max="2" width="6.21875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.28515625" customWidth="1"/>
+    <col min="2" max="2" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.85546875" bestFit="1" customWidth="1"/>
     <col min="4" max="5" width="12" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.140625" bestFit="1" customWidth="1"/>
     <col min="7" max="8" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B7" s="8"/>
       <c r="C7" s="8"/>
       <c r="D7" s="8" t="s">
@@ -1201,7 +1199,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B8" s="9" t="s">
         <v>27</v>
       </c>
@@ -1224,7 +1222,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B9" s="7" t="s">
         <v>64</v>
       </c>
@@ -1235,7 +1233,7 @@
       <c r="G9" s="6"/>
       <c r="H9" s="6"/>
     </row>
-    <row r="10" spans="1:8" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B10" s="5" t="s">
         <v>40</v>
       </c>
@@ -1258,7 +1256,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="1:8" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B11" s="5" t="s">
         <v>43</v>
       </c>
@@ -1281,7 +1279,7 @@
         <v>18.409090909090907</v>
       </c>
     </row>
-    <row r="12" spans="1:8" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B12" s="5" t="s">
         <v>45</v>
       </c>
@@ -1304,7 +1302,7 @@
         <v>8.6363636363636385</v>
       </c>
     </row>
-    <row r="13" spans="1:8" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:8" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B13" s="5" t="s">
         <v>47</v>
       </c>
@@ -1327,7 +1325,7 @@
         <v>4.6363636363636367</v>
       </c>
     </row>
-    <row r="14" spans="1:8" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:8" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B14" s="5" t="s">
         <v>49</v>
       </c>
@@ -1350,7 +1348,7 @@
         <v>8.5454545454545467</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="15" hidden="1" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:8" ht="15.75" hidden="1" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B15" s="3" t="s">
         <v>51</v>
       </c>
@@ -1373,13 +1371,13 @@
         <v>11.909090909090908</v>
       </c>
     </row>
-    <row r="16" spans="1:8" collapsed="1" x14ac:dyDescent="0.3"/>
-    <row r="18" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:8" collapsed="1" x14ac:dyDescent="0.25"/>
+    <row r="18" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B19" s="8"/>
       <c r="C19" s="8"/>
       <c r="D19" s="8" t="s">
@@ -1398,7 +1396,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="20" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B20" s="9" t="s">
         <v>27</v>
       </c>
@@ -1421,7 +1419,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B21" s="7" t="s">
         <v>65</v>
       </c>
@@ -1432,7 +1430,7 @@
       <c r="G21" s="6"/>
       <c r="H21" s="6"/>
     </row>
-    <row r="22" spans="1:8" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:8" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B22" s="5" t="s">
         <v>53</v>
       </c>
@@ -1455,7 +1453,7 @@
         <v>300.00000000000023</v>
       </c>
     </row>
-    <row r="23" spans="1:8" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:8" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B23" s="5" t="s">
         <v>57</v>
       </c>
@@ -1478,7 +1476,7 @@
         <v>1E+30</v>
       </c>
     </row>
-    <row r="24" spans="1:8" ht="15" hidden="1" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:8" ht="15.75" hidden="1" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B24" s="3" t="s">
         <v>61</v>
       </c>
@@ -1501,7 +1499,7 @@
         <v>1E+30</v>
       </c>
     </row>
-    <row r="25" spans="1:8" collapsed="1" x14ac:dyDescent="0.3"/>
+    <row r="25" spans="1:8" collapsed="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1510,43 +1508,43 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A15BD55B-445D-4DC8-BB54-9C064CB72DED}">
   <dimension ref="A1:J20"/>
-  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="1" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="2.33203125" customWidth="1"/>
-    <col min="2" max="2" width="5.21875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="26.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.28515625" customWidth="1"/>
+    <col min="2" max="2" width="5.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="2.33203125" customWidth="1"/>
+    <col min="5" max="5" width="2.28515625" customWidth="1"/>
     <col min="6" max="7" width="12" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="2.33203125" customWidth="1"/>
-    <col min="9" max="9" width="6.21875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="2.28515625" customWidth="1"/>
+    <col min="9" max="9" width="6.28515625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="9" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B6" s="8"/>
       <c r="C6" s="8" t="s">
         <v>72</v>
       </c>
       <c r="D6" s="8"/>
     </row>
-    <row r="7" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B7" s="9" t="s">
         <v>27</v>
       </c>
@@ -1557,7 +1555,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B8" s="3" t="s">
         <v>38</v>
       </c>
@@ -1568,8 +1566,8 @@
         <v>68.181818181818187</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B11" s="8"/>
       <c r="C11" s="8" t="s">
         <v>81</v>
@@ -1588,7 +1586,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="12" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B12" s="9" t="s">
         <v>27</v>
       </c>
@@ -1611,7 +1609,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B13" s="7" t="s">
         <v>64</v>
       </c>
@@ -1622,7 +1620,7 @@
       <c r="I13" s="6"/>
       <c r="J13" s="6"/>
     </row>
-    <row r="14" spans="1:10" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B14" s="5" t="s">
         <v>40</v>
       </c>
@@ -1645,7 +1643,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="15" spans="1:10" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B15" s="5" t="s">
         <v>43</v>
       </c>
@@ -1668,7 +1666,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="16" spans="1:10" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B16" s="5" t="s">
         <v>45</v>
       </c>
@@ -1691,7 +1689,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="17" spans="2:10" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:10" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B17" s="5" t="s">
         <v>47</v>
       </c>
@@ -1714,7 +1712,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="18" spans="2:10" hidden="1" outlineLevel="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:10" hidden="1" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="B18" s="5" t="s">
         <v>49</v>
       </c>
@@ -1737,7 +1735,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="19" spans="2:10" ht="15" hidden="1" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:10" ht="15.75" hidden="1" outlineLevel="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B19" s="3" t="s">
         <v>51</v>
       </c>
@@ -1760,7 +1758,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="20" spans="2:10" collapsed="1" x14ac:dyDescent="0.3"/>
+    <row r="20" spans="2:10" collapsed="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1769,15 +1767,15 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H9"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="4" max="4" width="13.6640625" customWidth="1"/>
-    <col min="5" max="5" width="12.109375" customWidth="1"/>
-    <col min="6" max="6" width="17.33203125" customWidth="1"/>
-    <col min="7" max="7" width="21.5546875" customWidth="1"/>
+    <col min="4" max="4" width="13.7109375" customWidth="1"/>
+    <col min="5" max="5" width="12.140625" customWidth="1"/>
+    <col min="6" max="6" width="17.28515625" customWidth="1"/>
+    <col min="7" max="7" width="21.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1799,7 +1797,7 @@
       <c r="G1" s="1"/>
       <c r="H1" s="10"/>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -1816,11 +1814,10 @@
         <v>2</v>
       </c>
       <c r="F2">
-        <v>3</v>
-      </c>
-      <c r="H2" s="11"/>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
@@ -1837,11 +1834,10 @@
         <v>12</v>
       </c>
       <c r="F3">
-        <v>24</v>
-      </c>
-      <c r="H3" s="11"/>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+        <v>4.25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>7</v>
       </c>
@@ -1858,11 +1854,10 @@
         <v>54</v>
       </c>
       <c r="F4">
-        <v>13</v>
-      </c>
-      <c r="H4" s="11"/>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>9</v>
       </c>
@@ -1879,11 +1874,10 @@
         <v>285</v>
       </c>
       <c r="F5">
-        <v>9</v>
-      </c>
-      <c r="H5" s="11"/>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+        <v>1.2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>11</v>
       </c>
@@ -1900,11 +1894,10 @@
         <v>22</v>
       </c>
       <c r="F6">
-        <v>20</v>
-      </c>
-      <c r="H6" s="11"/>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+        <v>5.8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>13</v>
       </c>
@@ -1921,16 +1914,13 @@
         <v>80</v>
       </c>
       <c r="F7">
-        <v>19</v>
-      </c>
-      <c r="H7" s="11"/>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+        <v>8.6999999999999993</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="10"/>
-      <c r="F8" s="11"/>
-      <c r="H8" s="11"/>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="10"/>
       <c r="G9" s="2"/>
     </row>
